--- a/public/templates/BIEN_BAN_NHAP_HANG.xlsx
+++ b/public/templates/BIEN_BAN_NHAP_HANG.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'BB NHẬP HÀNG'!$A$1:$M$28</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'BB NHẬP HÀNG'!$13:$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'BB NHẬP HÀNG'!$1:$14</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>

--- a/public/templates/BIEN_BAN_NHAP_HANG.xlsx
+++ b/public/templates/BIEN_BAN_NHAP_HANG.xlsx
@@ -864,6 +864,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F379C3-B36E-FA46-90ED-3D8D3F44DE72}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="31.5" customHeight="1"/>
   <cols>
@@ -1393,7 +1396,7 @@
     <mergeCell ref="F13:G13"/>
   </mergeCells>
   <pageMargins left="0.16" right="0.12" top="0.12" bottom="0.12" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="89" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="28" max="16383" man="1"/>
